--- a/01_Altium_Project/BOMs/PowerTower_AdapterUltrazohm_RS.xlsx
+++ b/01_Altium_Project/BOMs/PowerTower_AdapterUltrazohm_RS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilflingti66489\Documents\powertower_adapter_uz\01_Altium_Project\Project Outputs for PowerTower_AdapterUltrazohm\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilflingti66489\Documents\powertower_adapter_uz\01_Altium_Project\BOMs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB700A4-721B-4E0E-92A6-E2E386FED48B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC62813-3460-4190-B124-CA57CEE53007}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1522,11 +1522,11 @@
       <c r="F8" s="24"/>
       <c r="G8" s="48">
         <f ca="1">TODAY()</f>
-        <v>44344</v>
+        <v>44358</v>
       </c>
       <c r="H8" s="47">
         <f ca="1">NOW()</f>
-        <v>44344.661229166668</v>
+        <v>44358.585203240742</v>
       </c>
       <c r="I8" s="28"/>
       <c r="J8" s="28"/>
